--- a/seekurity-siem/projects/aig/03.설계/AIG_Log연동설계.xlsx
+++ b/seekurity-siem/projects/aig/03.설계/AIG_Log연동설계.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +53,12 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -115,8 +119,73 @@
         <bgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003D7EAA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -157,11 +226,34 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="003D7EAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -225,6 +317,58 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -590,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -598,11 +742,13 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -611,15 +757,15 @@
           <t>Seekurity SIEM Log Source 관리</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+      <c r="G1" s="27" t="n"/>
+      <c r="H1" s="27" t="n"/>
+      <c r="I1" s="27" t="n"/>
+      <c r="J1" s="27" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -627,19 +773,16 @@
           <t>필수 항목</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
           <t>추가 정보</t>
         </is>
       </c>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="28" t="inlineStr">
+        <is>
+          <t>수집 현황 (2026-08-23 실측)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -692,192 +835,1359 @@
           <t>담당자</t>
         </is>
       </c>
+      <c r="K3" s="29" t="inlineStr">
+        <is>
+          <t>수집 상태</t>
+        </is>
+      </c>
+      <c r="L3" s="29" t="inlineStr">
+        <is>
+          <t>금일 수집(건)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Endpoint Security</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Linux Server</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>AIG_SIEM_Host_Linux</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>10.1.30.4</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>문서상 대상아님이나 수집 검증용으로 유지 중</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>기타 장비</t>
+        </is>
+      </c>
+      <c r="I4" s="31" t="inlineStr"/>
+      <c r="J4" s="31" t="inlineStr"/>
+      <c r="K4" s="34" t="inlineStr">
+        <is>
+          <t>수집중</t>
+        </is>
+      </c>
+      <c r="L4" s="32" t="n">
+        <v>9058</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>Network Security</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Firewall</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Syslog</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>[샘플] Firewall-01</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>x.x.x.x</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>방화벽 로그</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>AIG_SSLVPN_FW</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>10.1.1.1</t>
+        </is>
+      </c>
+      <c r="F5" s="38" t="inlineStr">
+        <is>
+          <t>약 268 EPM. srcIp/dstIp/action 정규화 확인</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
+      <c r="H5" s="36" t="inlineStr">
+        <is>
+          <t>FortiGate 81F</t>
+        </is>
+      </c>
+      <c r="I5" s="36" t="inlineStr"/>
+      <c r="J5" s="36" t="inlineStr"/>
+      <c r="K5" s="34" t="inlineStr">
+        <is>
+          <t>수집중</t>
+        </is>
+      </c>
+      <c r="L5" s="37" t="n">
+        <v>16268</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>(미정)</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>211.47.6.115</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>SIEM 으로 Syslog 전송 중이나 FortiGate policy 35 에서 차단(621건). 차단 해제 후 형식 확인하여 등록 예정</t>
+        </is>
+      </c>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="I6" s="31" t="inlineStr"/>
+      <c r="J6" s="31" t="inlineStr"/>
+      <c r="K6" s="40" t="inlineStr">
+        <is>
+          <t>차단됨</t>
+        </is>
+      </c>
+      <c r="L6" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>AIG_GW01_Linux</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>211.47.20.230</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="inlineStr">
+        <is>
+          <t>장비 정상 가동. rsyslog/Filebeat 미설정</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr"/>
+      <c r="J7" s="36" t="inlineStr"/>
+      <c r="K7" s="41" t="inlineStr">
+        <is>
+          <t>미수신</t>
+        </is>
+      </c>
+      <c r="L7" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Endpoint Security</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Linux Server</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>AIG_WAS01_Linux</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>10.1.30.2</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>장비 정상 가동. rsyslog/Filebeat 미설정</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr"/>
+      <c r="J8" s="31" t="inlineStr"/>
+      <c r="K8" s="41" t="inlineStr">
+        <is>
+          <t>미수신</t>
+        </is>
+      </c>
+      <c r="L8" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Endpoint Security</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>Linux Server</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>AIG_WAS02_Linux</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>10.1.30.3</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="inlineStr">
+        <is>
+          <t>장비 정상 가동. rsyslog/Filebeat 미설정</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr"/>
+      <c r="J9" s="36" t="inlineStr"/>
+      <c r="K9" s="41" t="inlineStr">
+        <is>
+          <t>미수신</t>
+        </is>
+      </c>
+      <c r="L9" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Web Server</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>AIG_WEB01_Nginx</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>211.47.20.228</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>장비 정상 가동. rsyslog/Filebeat 미설정</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Nginx</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>Web Server</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="inlineStr"/>
+      <c r="J10" s="31" t="inlineStr"/>
+      <c r="K10" s="41" t="inlineStr">
+        <is>
+          <t>미수신</t>
+        </is>
+      </c>
+      <c r="L10" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Web Server</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>AIG_WEB02_Nginx</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>211.47.20.229</t>
+        </is>
+      </c>
+      <c r="F11" s="38" t="inlineStr">
+        <is>
+          <t>장비 정상 가동. rsyslog/Filebeat 미설정</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>Nginx</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>Web Server</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="inlineStr"/>
+      <c r="J11" s="36" t="inlineStr"/>
+      <c r="K11" s="41" t="inlineStr">
+        <is>
+          <t>미수신</t>
+        </is>
+      </c>
+      <c r="L11" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Network Security</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>IPS/IDS</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>L4 Switch</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Syslog</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>[샘플] IPS-01</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>x.x.x.x</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>IPS 로그</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Endpoint Security</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Windows Server</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Agent</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>[샘플] WinServer-01</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>x.x.x.x</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Windows Event Log</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Endpoint Security</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Linux Server</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>AIG_DMZ_L4</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>관리 IP 미확보</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>Piolink</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr"/>
+      <c r="I12" s="31" t="inlineStr"/>
+      <c r="J12" s="31" t="inlineStr"/>
+      <c r="K12" s="42" t="inlineStr">
+        <is>
+          <t>IP 미확보</t>
+        </is>
+      </c>
+      <c r="L12" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>Network Security</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>Firewall</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Syslog</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>[샘플] LinuxServer-01</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>x.x.x.x</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>Linux Syslog</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>AIG_FW</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="38" t="inlineStr">
+        <is>
+          <t>관리 IP 미확보</t>
+        </is>
+      </c>
+      <c r="G13" s="36" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="inlineStr">
+        <is>
+          <t>FortiGate</t>
+        </is>
+      </c>
+      <c r="I13" s="36" t="inlineStr"/>
+      <c r="J13" s="36" t="inlineStr"/>
+      <c r="K13" s="42" t="inlineStr">
+        <is>
+          <t>IP 미확보</t>
+        </is>
+      </c>
+      <c r="L13" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>Network Security</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>L4 Switch</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>AIG_INT_L4</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>관리 IP 미확보</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>Piolink</t>
+        </is>
+      </c>
+      <c r="H14" s="31" t="inlineStr"/>
+      <c r="I14" s="31" t="inlineStr"/>
+      <c r="J14" s="31" t="inlineStr"/>
+      <c r="K14" s="42" t="inlineStr">
+        <is>
+          <t>IP 미확보</t>
+        </is>
+      </c>
+      <c r="L14" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Network Security</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>IDS/IPS</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="inlineStr">
+        <is>
+          <t>AIG_IPS_VPN</t>
+        </is>
+      </c>
+      <c r="E15" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="38" t="inlineStr">
+        <is>
+          <t>관리 IP 미확보</t>
+        </is>
+      </c>
+      <c r="G15" s="36" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
+      <c r="H15" s="36" t="inlineStr">
+        <is>
+          <t>FortiGate</t>
+        </is>
+      </c>
+      <c r="I15" s="36" t="inlineStr"/>
+      <c r="J15" s="36" t="inlineStr"/>
+      <c r="K15" s="42" t="inlineStr">
+        <is>
+          <t>IP 미확보</t>
+        </is>
+      </c>
+      <c r="L15" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>Network Security</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>L3 Switch</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>AIG_L3_Switch</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>관리 IP 미확보</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="inlineStr"/>
+      <c r="I16" s="31" t="inlineStr"/>
+      <c r="J16" s="31" t="inlineStr"/>
+      <c r="K16" s="42" t="inlineStr">
+        <is>
+          <t>IP 미확보</t>
+        </is>
+      </c>
+      <c r="L16" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>Network Security</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>WAF</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>Syslog</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>AIG_WAF</t>
+        </is>
+      </c>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>관리 IP 미확보</t>
+        </is>
+      </c>
+      <c r="G17" s="36" t="inlineStr">
+        <is>
+          <t>모니터랩</t>
+        </is>
+      </c>
+      <c r="H17" s="36" t="inlineStr"/>
+      <c r="I17" s="36" t="inlineStr"/>
+      <c r="J17" s="36" t="inlineStr"/>
+      <c r="K17" s="42" t="inlineStr">
+        <is>
+          <t>IP 미확보</t>
+        </is>
+      </c>
+      <c r="L17" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Data &amp; Application</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Syslog</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>[샘플] DB-01</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>x.x.x.x</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Database Audit Log</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="inlineStr"/>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>(미정)</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>211.47.6.116</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>외부 DNS(8.8.8.8) 직접 질의 160건. 용도 확인 필요</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="inlineStr"/>
+      <c r="J18" s="31" t="inlineStr"/>
+      <c r="K18" s="43" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="L18" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="36" t="inlineStr">
+        <is>
+          <t>(미정)</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>211.47.6.118</t>
+        </is>
+      </c>
+      <c r="F19" s="38" t="inlineStr">
+        <is>
+          <t>10.1.10.4:10010 연동 502건. 용도 확인 필요</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="H19" s="36" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="I19" s="36" t="inlineStr"/>
+      <c r="J19" s="36" t="inlineStr"/>
+      <c r="K19" s="43" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="L19" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>(미정)</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>10.1.10.4</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>외부 SSH 및 211.47.6.116:3306 접근. 용도 확인 필요</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="I20" s="31" t="inlineStr"/>
+      <c r="J20" s="31" t="inlineStr"/>
+      <c r="K20" s="43" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="L20" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B21" s="36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="36" t="inlineStr">
+        <is>
+          <t>(미정)</t>
+        </is>
+      </c>
+      <c r="E21" s="36" t="inlineStr">
+        <is>
+          <t>211.47.6.119</t>
+        </is>
+      </c>
+      <c r="F21" s="38" t="inlineStr">
+        <is>
+          <t>NTP 소량. 용도 확인 필요</t>
+        </is>
+      </c>
+      <c r="G21" s="36" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="I21" s="36" t="inlineStr"/>
+      <c r="J21" s="36" t="inlineStr"/>
+      <c r="K21" s="43" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="L21" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>(미정)</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>211.47.6.125</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>NTP 소량. 용도 확인 필요</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="H22" s="31" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="I22" s="31" t="inlineStr"/>
+      <c r="J22" s="31" t="inlineStr"/>
+      <c r="K22" s="43" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="L22" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>(대상아님)</t>
+        </is>
+      </c>
+      <c r="E23" s="36" t="inlineStr">
+        <is>
+          <t>10.1.20.2</t>
+        </is>
+      </c>
+      <c r="F23" s="38" t="inlineStr">
+        <is>
+          <t>문서상 대상아님</t>
+        </is>
+      </c>
+      <c r="G23" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="36" t="inlineStr"/>
+      <c r="J23" s="36" t="inlineStr"/>
+      <c r="K23" s="44" t="inlineStr">
+        <is>
+          <t>대상아님</t>
+        </is>
+      </c>
+      <c r="L23" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>(대상아님)</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>10.1.20.3</t>
+        </is>
+      </c>
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>문서상 대상아님</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="31" t="inlineStr"/>
+      <c r="J24" s="31" t="inlineStr"/>
+      <c r="K24" s="44" t="inlineStr">
+        <is>
+          <t>대상아님</t>
+        </is>
+      </c>
+      <c r="L24" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>(대상아님)</t>
+        </is>
+      </c>
+      <c r="E25" s="36" t="inlineStr">
+        <is>
+          <t>10.1.20.5</t>
+        </is>
+      </c>
+      <c r="F25" s="38" t="inlineStr">
+        <is>
+          <t>문서상 대상아님</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="36" t="inlineStr"/>
+      <c r="J25" s="36" t="inlineStr"/>
+      <c r="K25" s="44" t="inlineStr">
+        <is>
+          <t>대상아님</t>
+        </is>
+      </c>
+      <c r="L25" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>(대상아님)</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>10.1.20.10</t>
+        </is>
+      </c>
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>문서상 대상아님</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="31" t="inlineStr"/>
+      <c r="J26" s="31" t="inlineStr"/>
+      <c r="K26" s="44" t="inlineStr">
+        <is>
+          <t>대상아님</t>
+        </is>
+      </c>
+      <c r="L26" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="36" t="inlineStr">
+        <is>
+          <t>(대상아님)</t>
+        </is>
+      </c>
+      <c r="E27" s="36" t="inlineStr">
+        <is>
+          <t>10.1.40.2</t>
+        </is>
+      </c>
+      <c r="F27" s="38" t="inlineStr">
+        <is>
+          <t>문서상 대상아님</t>
+        </is>
+      </c>
+      <c r="G27" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="36" t="inlineStr"/>
+      <c r="J27" s="36" t="inlineStr"/>
+      <c r="K27" s="44" t="inlineStr">
+        <is>
+          <t>대상아님</t>
+        </is>
+      </c>
+      <c r="L27" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>(대상아님)</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>10.1.40.3</t>
+        </is>
+      </c>
+      <c r="F28" s="33" t="inlineStr">
+        <is>
+          <t>문서상 대상아님</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="31" t="inlineStr"/>
+      <c r="J28" s="31" t="inlineStr"/>
+      <c r="K28" s="44" t="inlineStr">
+        <is>
+          <t>대상아님</t>
+        </is>
+      </c>
+      <c r="L28" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>Data &amp; Application</t>
+        </is>
+      </c>
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>(대상아님)</t>
+        </is>
+      </c>
+      <c r="E29" s="36" t="inlineStr">
+        <is>
+          <t>10.1.40.4</t>
+        </is>
+      </c>
+      <c r="F29" s="38" t="inlineStr">
+        <is>
+          <t>문서상 대상아님</t>
+        </is>
+      </c>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="36" t="inlineStr"/>
+      <c r="J29" s="36" t="inlineStr"/>
+      <c r="K29" s="44" t="inlineStr">
+        <is>
+          <t>대상아님</t>
+        </is>
+      </c>
+      <c r="L29" s="37" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="F2:J2"/>
   </mergeCells>
   <dataValidations count="2">
